--- a/чек-лист.xlsx
+++ b/чек-лист.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\арх зачет заданиие\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishukdn\OneDrive\!Материалы КЭТ\27. Архитектура-Андрианов\Зачет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3303A1DD-3772-4B94-8349-5EED24DE4007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A02EC8-C9E8-47BF-927B-0693742A762F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="1032" windowWidth="17280" windowHeight="10044" xr2:uid="{4D2451AB-8DE5-4CF7-9623-478264A7A8F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4D2451AB-8DE5-4CF7-9623-478264A7A8F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -27,16 +27,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -314,7 +306,7 @@
     <t>Ваша Фамилия и вариант:</t>
   </si>
   <si>
-    <t>Ложкин Иван 8 вариант</t>
+    <t>Митрофан?</t>
   </si>
 </sst>
 </file>
@@ -527,9 +519,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -567,7 +559,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -673,7 +665,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -815,7 +807,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -824,16 +816,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B21F763-96BE-4D72-A761-49FD90F8CA23}">
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="47.88671875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>86</v>
       </c>
@@ -842,16 +834,16 @@
       </c>
       <c r="D1" s="9">
         <f>SUM(чек_лист[Column1])</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -868,7 +860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -879,14 +871,14 @@
         <v>6</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -897,14 +889,14 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -915,14 +907,14 @@
         <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -940,7 +932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -958,7 +950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -976,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,7 +986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1012,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1030,7 +1022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1048,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1066,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1102,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1120,7 +1112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1138,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -1156,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1174,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -1192,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1210,7 +1202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1228,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1246,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1264,7 +1256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1282,7 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -1300,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1318,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
@@ -1336,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1354,7 +1346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -1372,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -1390,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1408,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -1426,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
@@ -1444,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1462,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -1480,7 +1472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -1498,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -1516,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1534,7 +1526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -1552,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -1570,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -1588,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -1606,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -1624,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -1642,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -1660,7 +1652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -1678,7 +1670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -1696,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>52</v>
       </c>
@@ -1714,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -1732,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -1750,7 +1742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -1768,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>56</v>
       </c>
@@ -1786,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -1804,7 +1796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>60</v>
       </c>
@@ -1822,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>62</v>
       </c>
@@ -1840,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1858,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>66</v>
       </c>
@@ -1876,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1894,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>66</v>
       </c>
@@ -1912,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -1930,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>70</v>
       </c>
@@ -1948,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1966,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>70</v>
       </c>
@@ -1984,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>70</v>
       </c>
@@ -2002,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>76</v>
       </c>
@@ -2020,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -2038,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
@@ -2067,7 +2059,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7456C1-2095-4BDB-BA2C-94F89119F695}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/чек-лист.xlsx
+++ b/чек-лист.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishukdn\OneDrive\!Материалы КЭТ\27. Архитектура-Андрианов\Зачет\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\architect_ivan_var_8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A02EC8-C9E8-47BF-927B-0693742A762F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B60FFD-A720-49FF-BE51-561AC0B33763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4D2451AB-8DE5-4CF7-9623-478264A7A8F6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="13800" xr2:uid="{4D2451AB-8DE5-4CF7-9623-478264A7A8F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -27,8 +27,16 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -306,7 +314,7 @@
     <t>Ваша Фамилия и вариант:</t>
   </si>
   <si>
-    <t>Митрофан?</t>
+    <t>Ложкин Иван, 3-1Ис, 8 вариант</t>
   </si>
 </sst>
 </file>
@@ -519,9 +527,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -559,7 +567,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -665,7 +673,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -807,7 +815,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -816,16 +824,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B21F763-96BE-4D72-A761-49FD90F8CA23}">
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="47.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="47.88671875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>86</v>
       </c>
@@ -834,16 +842,16 @@
       </c>
       <c r="D1" s="9">
         <f>SUM(чек_лист[Column1])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -860,7 +868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,14 +879,14 @@
         <v>6</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -889,14 +897,14 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -907,14 +915,14 @@
         <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -925,14 +933,14 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,14 +951,14 @@
         <v>6</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -961,14 +969,14 @@
         <v>6</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -979,14 +987,14 @@
         <v>6</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -997,14 +1005,14 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1015,14 +1023,14 @@
         <v>6</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1040,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1058,7 +1066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1069,14 +1077,14 @@
         <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1087,14 +1095,14 @@
         <v>18</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1105,14 +1113,14 @@
         <v>18</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1123,14 +1131,14 @@
         <v>18</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -1141,14 +1149,14 @@
         <v>6</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1159,14 +1167,14 @@
         <v>6</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -1177,14 +1185,14 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1195,14 +1203,14 @@
         <v>6</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1213,14 +1221,14 @@
         <v>6</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1231,14 +1239,14 @@
         <v>6</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1249,14 +1257,14 @@
         <v>6</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1267,14 +1275,14 @@
         <v>6</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -1285,14 +1293,14 @@
         <v>6</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1303,14 +1311,14 @@
         <v>6</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
@@ -1321,14 +1329,14 @@
         <v>18</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1339,14 +1347,14 @@
         <v>18</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -1357,14 +1365,14 @@
         <v>6</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -1375,14 +1383,14 @@
         <v>6</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1393,14 +1401,14 @@
         <v>6</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -1411,14 +1419,14 @@
         <v>6</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
@@ -1429,14 +1437,14 @@
         <v>6</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1447,14 +1455,14 @@
         <v>6</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -1472,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -1490,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -1508,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1519,14 +1527,14 @@
         <v>6</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -1537,14 +1545,14 @@
         <v>6</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -1555,14 +1563,14 @@
         <v>18</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -1573,14 +1581,14 @@
         <v>18</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -1591,14 +1599,14 @@
         <v>18</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -1609,14 +1617,14 @@
         <v>18</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -1627,14 +1635,14 @@
         <v>18</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -1645,14 +1653,14 @@
         <v>18</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -1663,14 +1671,14 @@
         <v>6</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -1681,14 +1689,14 @@
         <v>6</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>52</v>
       </c>
@@ -1699,14 +1707,14 @@
         <v>2</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -1717,14 +1725,14 @@
         <v>1</v>
       </c>
       <c r="D51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -1735,14 +1743,14 @@
         <v>2</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -1753,14 +1761,14 @@
         <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>56</v>
       </c>
@@ -1771,14 +1779,14 @@
         <v>6</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -1789,14 +1797,14 @@
         <v>6</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>60</v>
       </c>
@@ -1807,14 +1815,14 @@
         <v>6</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>62</v>
       </c>
@@ -1825,14 +1833,14 @@
         <v>6</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1843,14 +1851,14 @@
         <v>18</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>66</v>
       </c>
@@ -1861,14 +1869,14 @@
         <v>6</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1879,14 +1887,14 @@
         <v>6</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>66</v>
       </c>
@@ -1897,14 +1905,14 @@
         <v>18</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -1915,14 +1923,14 @@
         <v>1</v>
       </c>
       <c r="D62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>70</v>
       </c>
@@ -1933,14 +1941,14 @@
         <v>6</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1951,14 +1959,14 @@
         <v>6</v>
       </c>
       <c r="D64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>70</v>
       </c>
@@ -1969,14 +1977,14 @@
         <v>18</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>70</v>
       </c>
@@ -1987,14 +1995,14 @@
         <v>18</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>76</v>
       </c>
@@ -2012,7 +2020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -2030,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
@@ -2059,7 +2067,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7456C1-2095-4BDB-BA2C-94F89119F695}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/чек-лист.xlsx
+++ b/чек-лист.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\architect_ivan_var_8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B60FFD-A720-49FF-BE51-561AC0B33763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFC2BE1-6F18-41A4-BA06-BF50E6F8CC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="13800" xr2:uid="{4D2451AB-8DE5-4CF7-9623-478264A7A8F6}"/>
   </bookViews>
@@ -842,7 +842,7 @@
       </c>
       <c r="D1" s="9">
         <f>SUM(чек_лист[Column1])</f>
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1473,11 +1473,11 @@
         <v>6</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,11 +1491,11 @@
         <v>6</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1509,11 +1509,11 @@
         <v>6</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -2013,11 +2013,11 @@
         <v>18</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -2031,11 +2031,11 @@
         <v>18</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <f>чек_лист[[#This Row],[Выполнение (1 или 0) ЗАПОЛНЯЕМ]]*чек_лист[[#This Row],[Баллы (0-2)]]</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
